--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist, Commercial Analytics</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67abc49b6fa8476</t>
+          <t>https://www.indeed.com/viewjob?jk=ddb5e4ec7eea6d12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, AKS, CI/CD, Snowflake, Power BI, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0de17ce9a6114c</t>
+          <t>https://www.indeed.com/viewjob?jk=be33ec36f2c230a0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,52 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e59a111139bd8b0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38349e76a7b526d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2abea4aa18f44f80</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,77 +496,182 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb5e4ec7eea6d12</t>
+          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Analytics and Research Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Serco</t>
+          <t>Bonterra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
+          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be33ec36f2c230a0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e17e875da176c38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Data Engineer - ITS4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>State of Minnesota - Minnesota IT Services</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Git, Redshift, PySpark, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AI Lab Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Berkeley Research Group, LLC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1020cf6bf633af55</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8114133a7605a0ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Senior Data Analytics and Research Analyst</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Serco</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Herndon, VA, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2abea4aa18f44f80</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79e25aff465dcd7c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Architect AI Engineer with AWS Skills Charlotte NC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>IPolarity LLC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>12.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ee93c84147c4e9c</t>
+          <t>https://www.indeed.com/viewjob?jk=63b67a79a062cab9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solutions Architect, Agentic AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bonterra</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>Generative AI, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e17e875da176c38</t>
+          <t>https://www.indeed.com/viewjob?jk=818dde8141f9c7e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Senior Software Engineer, Test Infrastructure Development</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Git, Redshift, PySpark, NoSQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,112 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb33eaf3683a2fd9</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Lab Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Berkeley Research Group, LLC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1020cf6bf633af55</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Databricks, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8114133a7605a0ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79e25aff465dcd7c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e65a16ec81d395d</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Architect AI Engineer with AWS Skills Charlotte NC</t>
+          <t>Senior Quantitative Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Aktra Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63b67a79a062cab9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect, Agentic AI</t>
+          <t>LoopNet - Software Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Optimization</t>
+          <t>RAG, Copilot, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,987 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=818dde8141f9c7e9</t>
+          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Test Infrastructure Development</t>
+          <t>Specialist Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Agilify</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, S3, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Kafka</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Architect (Azure + Databricks)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nine Core Technologies</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Databricks, PySpark, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c55aadfc7fd1db</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fcb32206714a459d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34a7f24f37796f5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2f52987f0a9614b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer Backend Systems</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, FastAPI, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Berkshire Hathaway Specialty Insurance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Decision Scientist – Fulfillment Analytics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Best Buy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90bf434c39d78927</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6e627292095fd15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ead38b1b4852870b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Streaming</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rivian and Volkswagen Group Technologies</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Engineer II, Software Assurance, Product Security (Remote)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb59d32d4fcbcc21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NAVEX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d504a327d8f9724d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NAVEX</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lake Oswego, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f69cd42922703ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LogicMonitor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist – Artificial Intelligence &amp; Manufacturing Analytics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRPDG</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Juncos, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b72ee37f3a47ee9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer 5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e65a16ec81d395d</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4b4dbab145e9f3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Observability Engineer AIOPS Splunk</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Formac Inc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Jenkins, GitHub Actions, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=151f58b112bf3436</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RoadSync</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0cdecaf978859315</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Eng</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3792e053b69a402f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist - Strategic Network Design</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Best Buy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c07e8dca8ce7ee34</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Glendale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, LightGBM, Git, Snowflake, Databricks, Python, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a31ce8c91f66435</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Quantitative Developer</t>
+          <t>Data Scientist (AI/ML)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aktra Inc</t>
+          <t>Georgia Transmission Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tucker, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, LangChain, RAG, FAISS, Prompt Engineering, TensorFlow, PyTorch, Synapse, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6a4d190221fd911</t>
+          <t>https://www.indeed.com/viewjob?jk=813deb7f65cc68d5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LoopNet - Software Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51f6585eaae3edd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specialist Software Engineer</t>
+          <t>Architect Network Automation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>OnX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf053b4e78a7784</t>
+          <t>https://www.indeed.com/viewjob?jk=3582b7d646e4ea1d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PySpark, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, BigQuery, BigQuery, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07c6726c35ad8fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=aafe4abda47c5317</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Solution Engineer</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Agilify</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, BigQuery, Kubernetes, CI/CD, GitHub Actions, Git, BigQuery, Kafka</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=173deae55fc0fc11</t>
+          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Full Stack Engineer (Payments)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2526f9ca235bb42c</t>
+          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Informatica Cloud Data Engineer (IDMC/IICS)</t>
+          <t>Senior Applied Value Engineer – Automotive Manufacturing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Celonis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f156bc316e4a8e1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8e7f37434e4210</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect (Azure + Databricks)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nine Core Technologies</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milpitas, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Terraform, Databricks, PySpark, Kafka, Python, SQL</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=118ef7e12d0743d7</t>
+          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c55aadfc7fd1db</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2af7b500b42a69</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Architect, Data (Remote US)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Atmosera</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Synapse, Git, Databricks, Power BI, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb32206714a459d</t>
+          <t>https://www.indeed.com/viewjob?jk=218af96edb0c06d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer (Human-Led AI Orchestration + Action Points)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SERVANT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>AI Engineer, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a7f24f37796f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=51169ce337352ff7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,637 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f52987f0a9614b</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer Backend Systems</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Health Data Analytics Institute</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Dedham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, FastAPI, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=620bf1fdfb70a395</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9e4130f1298022</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7f7784d943297ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Decision Scientist – Fulfillment Analytics</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Best Buy</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90bf434c39d78927</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e627292095fd15</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, MongoDB, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ead38b1b4852870b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Streaming</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rivian and Volkswagen Group Technologies</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3871dec46927667b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Engineer II, Software Assurance, Product Security (Remote)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, S3, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb59d32d4fcbcc21</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NAVEX</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d504a327d8f9724d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NAVEX</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lake Oswego, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Terraform, Git, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cd42922703ba9</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LogicMonitor</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=92a2dfe6bebcb2dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr Data Scientist – Artificial Intelligence &amp; Manufacturing Analytics</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PRPDG</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Juncos, PR, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, OpenCV, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b72ee37f3a47ee9</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Software Development Engineer 5</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Adobe</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d4b4dbab145e9f3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Observability Engineer AIOPS Splunk</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Formac Inc</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Jenkins, GitHub Actions, Terraform, Git, Kafka, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=151f58b112bf3436</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>RoadSync</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, S3, EC2, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0cdecaf978859315</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Eng</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>UKG</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3792e053b69a402f</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Data Scientist - Strategic Network Design</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Best Buy</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Data Scientist, PySpark, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c07e8dca8ce7ee34</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Glendale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, LightGBM, Git, Snowflake, Databricks, Python, R, Scala, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a31ce8c91f66435</t>
+          <t>https://www.indeed.com/viewjob?jk=bd5bd9348fb676a9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist (AI/ML)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Georgia Transmission Corporation</t>
+          <t>megan soft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tucker, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, FAISS, Prompt Engineering, TensorFlow, PyTorch, Synapse, MLflow, FastAPI</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=813deb7f65cc68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. SW Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0844aea628b28dab</t>
+          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Architect Network Automation</t>
+          <t>Cybersecurity Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OnX</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Copilot, S3, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3582b7d646e4ea1d</t>
+          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Elanco</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, BigQuery, BigQuery, Matplotlib, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aafe4abda47c5317</t>
+          <t>https://www.indeed.com/viewjob?jk=9086dcab71885510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7956002449dfcaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=46f389e673d542e4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer (Payments)</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3915e239710ba577</t>
+          <t>https://www.indeed.com/viewjob?jk=f9cbf0c5799899cb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Applied Value Engineer – Automotive Manufacturing</t>
+          <t>DevOps Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Celonis</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, Git, Databricks, Python, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8e7f37434e4210</t>
+          <t>https://www.indeed.com/viewjob?jk=365a2a5b6e1aa678</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Enterprise Systems Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Schellman</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29325c8c8e335924</t>
+          <t>https://www.indeed.com/viewjob?jk=24f21b13a63ee546</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer, Contract To Hire</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Git, PySpark, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2af7b500b42a69</t>
+          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution Architect, Data (Remote US)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Atmosera</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Synapse, Git, Databricks, Power BI, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=218af96edb0c06d2</t>
+          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer (Human-Led AI Orchestration + Action Points)</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SERVANT</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,777 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51169ce337352ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Development Engineer</t>
+          <t>Senior Amazon Connect Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>TELUS Digital</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Amazon Connect Application Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TELUS Digital</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Charlottesville, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Agentic Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, MLflow, Docker, Kubernetes, Jenkins, Databricks, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f90afcb48c2da717</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Operations Engineer, BizTech</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Astre Consulting Services</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4d3b3a89a0ecdfc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MDM Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Temple, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer ( Seattle/Provo)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Press Ganey</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80c62548a6630d96</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Developer - Virtualization and SIL Integration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Milford, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=feff71f2ce1f4d3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Sr. Business Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Crane Worldwide Logistics</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Engineer, Corp Solutions</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Papa John's</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - Java</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>REAL Broker, LLC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e786795d10430cb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pisces Healthcare Solutions</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Winchester, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, MLflow, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=766cb467c7e6c2e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Scientist (E5242C)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IEEE Corporate</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5a15c7a69af3aec</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Foley</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5bd9348fb676a9</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, S3, Glue, Redshift, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SpyCloud</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, Data Lake, Terraform, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Engineer III</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ross Dress For Less</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Dublin, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15f1ad1f33250f88</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Test Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5231857c0cbbf172</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Sr. Test Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11b644f15c1c999c</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer II / Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Pelham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, PostgreSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21c2ae190bc7302f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Analyst/Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a47e73a151fa0319</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-20.xlsx
+++ b/daily_matches/job_matches_2026-07-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>megan soft</t>
+          <t>iSynergy IT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, TensorFlow, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, Glue, Redshift, BigQuery, Synapse, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74f99ec032c2a050</t>
+          <t>https://www.indeed.com/viewjob?jk=64aa04af21957dc5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>AI Software Engineer IV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Standard Insurance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, MLflow, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f774d387b35a5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c232645c82fc83</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cybersecurity Engineer</t>
+          <t>AI Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, Docker, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=278c7726eee6f36f</t>
+          <t>https://www.indeed.com/viewjob?jk=337ebeb99f027b5a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Elanco</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Synapse, CI/CD, Git, Databricks, Tableau, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9086dcab71885510</t>
+          <t>https://www.indeed.com/viewjob?jk=2cdfcb7d4f8c3b02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Agentic Solutions Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Data Lake, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f389e673d542e4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf96f48a943debeb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>bp</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, CI/CD, Git, Hadoop, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9cbf0c5799899cb</t>
+          <t>https://www.indeed.com/viewjob?jk=613724c65295aac4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Software Engineer</t>
+          <t>AI Engineer - Senior</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=365a2a5b6e1aa678</t>
+          <t>https://www.indeed.com/viewjob?jk=cafc10f66e77741c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Systems Architect</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Schellman</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Kinesis, Docker, Kubernetes, Terraform, Git, Kafka, R</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f21b13a63ee546</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1000fe76fc7bec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, PySpark, Kafka, PostgreSQL, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9eed61967883578e</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d1f01448956ac8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feceaa7f623de4d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9d86fee622b07b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Senior Azure Automation Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Stefanini North America and APAC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef89c4f9800f8a90</t>
+          <t>https://www.indeed.com/viewjob?jk=d3a616f5a94c37ef</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc58207e473b9f5</t>
+          <t>https://www.indeed.com/viewjob?jk=60db44428bef76ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Kafka, Hadoop, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f8bb981d509050f</t>
+          <t>https://www.indeed.com/viewjob?jk=d94c95081afe04c8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Amazon Connect Application Architect</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charlottesville, VA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kinesis, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>RAG, Data Lake, Jenkins, Terraform, Git, Databricks, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3612752c893190</t>
+          <t>https://www.indeed.com/viewjob?jk=4448bee09655101c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Agentic Solutions Engineer</t>
+          <t>Graph Developers/Engineers with Neo4j - (100% Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Syncreon Consulting</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, MLflow, Docker, Kubernetes, Jenkins, Databricks, Python, R, Java</t>
+          <t>RAG, Docker, CI/CD, NoSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f90afcb48c2da717</t>
+          <t>https://www.indeed.com/viewjob?jk=aa33836b9c42aa48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Operations Engineer, BizTech</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Tableau, Python, SQL, R</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40f9eb2ccac23ae0</t>
+          <t>https://www.indeed.com/viewjob?jk=c05da2cfeab851a7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Astre Consulting Services</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Terraform, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4d3b3a89a0ecdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=c92bf42340089b84</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Sr ML Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, SQL, R, Java</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3b598b8c3673649</t>
+          <t>https://www.indeed.com/viewjob?jk=845e6f6a446e1e35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer ( Seattle/Provo)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Press Ganey</t>
+          <t>Safeway</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b27efa8ed4a1f97</t>
+          <t>https://www.indeed.com/viewjob?jk=94c4f57796c1a77d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Safeway</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, MLflow, CI/CD, Databricks, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,462 +1161,42 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80c62548a6630d96</t>
+          <t>https://www.indeed.com/viewjob?jk=25898f2307268e0b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Developer - Virtualization and SIL Integration</t>
+          <t>Senior Associate, Data Scientist - Model Risk Office</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, Jenkins, Git, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, PyTorch, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=feff71f2ce1f4d3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sr. Business Intelligence Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Crane Worldwide Logistics</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53344a199a269470</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Corp Solutions</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Papa John's</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae25ca0f2bd81f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - Java</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>REAL Broker, LLC</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, NoSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e786795d10430cb1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pisces Healthcare Solutions</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Winchester, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, MLflow, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=766cb467c7e6c2e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Data Scientist (E5242C)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>IEEE Corporate</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a15c7a69af3aec</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Foley</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Redshift, Redshift, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb528101e5b7e6f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SpyCloud</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, S3, Data Lake, Terraform, Databricks, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b990fe917577735</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Engineer III</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ross Dress For Less</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Dublin, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15f1ad1f33250f88</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sr. Test Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5231857c0cbbf172</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Sr. Test Engineer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>10</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, CI/CD, NoSQL, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=11b644f15c1c999c</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Software Engineer II / Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Pelham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Git, PostgreSQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21c2ae190bc7302f</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Analyst/Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Quest Global</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a47e73a151fa0319</t>
+          <t>https://www.indeed.com/viewjob?jk=96f7142945ff184e</t>
         </is>
       </c>
     </row>
